--- a/templates/sales-approval.xlsx
+++ b/templates/sales-approval.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DHKIM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jangjingang/dev/smerp_next/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF8305A8-12A3-4BD1-AABD-9581EAEE16F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B71EE57-FE0C-6C41-A4E0-654B960BE2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2490" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SALES" sheetId="2" r:id="rId1"/>
@@ -18,17 +18,28 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">SALES!$B$2:$M$35</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>End User</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -160,171 +171,6 @@
   <si>
     <t>매입금액 합계(VAT포함)</t>
     <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>김대훈</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>*** 퀵/택배는 월간리스트에서 맞으면 관리부에서 매입 한번에 기록</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[품목명]
-예시_서버랙</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
-    <t>[품목명]
-예시_전원</t>
-    <phoneticPr fontId="33" type="noConversion"/>
-  </si>
-  <si>
-    <t>견적 나간 회사 / 해당 담당자 / 담당자 연락처</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>[매출처 앞단의 회사 정보가 공개 될 경우에 작성 / 없으면 미작성 or 매출처명]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> -19인치표준랙 (ANSI/EIA-310-D 규격)
- -(H)2,000*(W)600*(D)1,070 mm / 42U /Black
- -케이지너트 타입 마운트프레임( 유닛넘버링)
- -재질: SPCC 냉간압연강판
- -두께 : 1.2T, 1.5T, 2.0T
- -전면도어 : 벌집타공도어 &amp; 스윙핸들 잠금장치
- -후면도어 : 양문형 벌집타공도어 &amp; 스윙핸들 잠금장치
- -사이드판넬 : 스틸판넬 * 4개  ( 별도포장납품 )
- -하중선반 :  선반 2개
- -전원 : -</t>
-  </si>
-  <si>
-    <t>[제품명]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AL 10구 16A MCCB 랙전원
-&gt;단상3선식, 220V, 30A 배선용차단기(MCCB), 단자대
-&gt;3C*4.0SQ*2.5M
-&gt;출력소켓 : KS 타입소켓 * 10개
-&gt;입력플러그 : 220V 16A IP67 플러그(TYP 290)
-&gt;인입선용 소켓 : 220V 16A IP67 소켓(TYP 552) 제공</t>
-  </si>
-  <si>
-    <t>BYC, 1층 인도조건, 배송기사 1인, 하차 시 도움필요</t>
-  </si>
-  <si>
-    <t>RACK 코리아</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>예시_배송기사 별도 납품</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>매출처 측으로 발주서 받기 전 협의 or 납품 이후 발행</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[매출처 측 계산서 이메일]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[견적서의 결제조건으로 따라감] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>예시_계산서 발행 후 익월 말 현금 조건</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">[발주 시에 협의 후 정해지지만, 도중 배송 주소 변경 될 경우도 있음] </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>예시_가산디지털1로 131 BYC하이시티 B동 12층 1201호, 서버메이트</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>받는 사람의 이름 / 연락처</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[딜리버리가 정해져있을 경우 작성 / 딜리버리가 불분명 할 경우 별도협의 작성, 이후 서버메이트 사무실로 입고 시 협의 후 납품]</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[코드 순서-&gt;품의자이니셜/품의날짜/품의작성 날의 품의서 순서]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 예시_D251202-01</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[서버나 스토리지 등의 모델타입, 시리얼넘버가 있을 경우]</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color indexed="8"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 서버의 경우 예시_3A4BCTO1WW / S123Q1W2</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -332,12 +178,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="177" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="35">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,13 +438,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="돋움"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -988,20 +827,20 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="29" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1082,7 +921,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="14" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1142,7 +981,7 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="26" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1151,7 +990,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1166,64 +1005,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="21" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="2" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="21" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="6" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="4" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="4" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="24" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="19" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="20" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="20" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="15" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="20" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="20" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="15" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="4" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="4" borderId="8" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="23" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="23" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="3" borderId="0" xfId="6" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1232,67 +1071,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="14" fillId="5" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="14" fillId="5" borderId="6" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="19" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="18" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="18" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="21" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="21" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="2" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="14" fillId="5" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="5" borderId="9" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="24" fillId="5" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="19" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="5" borderId="12" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="19" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="2" borderId="22" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="2" borderId="22" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1310,10 +1149,10 @@
     <xf numFmtId="0" fontId="24" fillId="6" borderId="11" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="24" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="6" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="24" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="24" fillId="6" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="5" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1331,7 +1170,7 @@
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="35" fillId="5" borderId="0" xfId="7" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="34" fillId="5" borderId="0" xfId="7" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1361,61 +1200,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>56951</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>36314</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1208246</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>762000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{007C1567-E650-3FBC-7055-4FF774FC9008}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11815034" y="8725231"/>
-          <a:ext cx="1157645" cy="725686"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1685,25 +1469,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:P35"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="3" max="3" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="76.1640625" customWidth="1"/>
-    <col min="5" max="5" width="5.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.5" style="52" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" style="52" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.58203125" customWidth="1"/>
-    <col min="9" max="10" width="16.58203125" customWidth="1"/>
-    <col min="11" max="11" width="16.58203125" style="52" customWidth="1"/>
-    <col min="12" max="12" width="17.25" style="52" customWidth="1"/>
+    <col min="8" max="8" width="19.5" customWidth="1"/>
+    <col min="9" max="10" width="16.5" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="52" customWidth="1"/>
+    <col min="12" max="12" width="17.1640625" style="52" customWidth="1"/>
     <col min="13" max="13" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:13" ht="18" thickBot="1"/>
+    <row r="2" spans="2:13">
       <c r="B2" s="17"/>
       <c r="C2" s="18"/>
       <c r="D2" s="18"/>
@@ -1717,7 +1501,7 @@
       <c r="L2" s="53"/>
       <c r="M2" s="19"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:13">
       <c r="B3" s="12"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1731,7 +1515,7 @@
       <c r="L3" s="54"/>
       <c r="M3" s="20"/>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:13">
       <c r="B4" s="12"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -1745,7 +1529,7 @@
       <c r="L4" s="54"/>
       <c r="M4" s="20"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:13">
       <c r="B5" s="12"/>
       <c r="C5" s="96" t="s">
         <v>25</v>
@@ -1761,7 +1545,7 @@
       <c r="L5" s="96"/>
       <c r="M5" s="20"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:13">
       <c r="B6" s="12"/>
       <c r="C6" s="96"/>
       <c r="D6" s="96"/>
@@ -1775,7 +1559,7 @@
       <c r="L6" s="96"/>
       <c r="M6" s="20"/>
     </row>
-    <row r="7" spans="2:13" ht="39.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:13" ht="40">
       <c r="B7" s="12"/>
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
@@ -1789,7 +1573,7 @@
       <c r="L7" s="55"/>
       <c r="M7" s="20"/>
     </row>
-    <row r="8" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:13" ht="18">
       <c r="B8" s="12"/>
       <c r="C8" s="36" t="s">
         <v>23</v>
@@ -1805,14 +1589,12 @@
       <c r="L8" s="56"/>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:13" ht="18">
       <c r="B9" s="12"/>
       <c r="C9" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="29" t="s">
-        <v>51</v>
-      </c>
+      <c r="D9" s="29"/>
       <c r="E9" s="2"/>
       <c r="F9" s="56"/>
       <c r="G9" s="56"/>
@@ -1823,14 +1605,12 @@
       <c r="L9" s="56"/>
       <c r="M9" s="20"/>
     </row>
-    <row r="10" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:13" ht="18">
       <c r="B10" s="12"/>
       <c r="C10" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="29">
-        <v>45993</v>
-      </c>
+      <c r="D10" s="29"/>
       <c r="E10" s="2"/>
       <c r="F10" s="56"/>
       <c r="G10" s="56"/>
@@ -1841,14 +1621,12 @@
       <c r="L10" s="56"/>
       <c r="M10" s="20"/>
     </row>
-    <row r="11" spans="2:13" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:13" ht="18">
       <c r="B11" s="12"/>
       <c r="C11" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="30" t="s">
-        <v>33</v>
-      </c>
+      <c r="D11" s="30"/>
       <c r="E11" s="3"/>
       <c r="F11" s="57"/>
       <c r="G11" s="57"/>
@@ -1859,7 +1637,7 @@
       <c r="L11" s="57"/>
       <c r="M11" s="20"/>
     </row>
-    <row r="12" spans="2:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:13" ht="23.25" customHeight="1">
       <c r="B12" s="12"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
@@ -1873,14 +1651,12 @@
       <c r="L12" s="74"/>
       <c r="M12" s="20"/>
     </row>
-    <row r="13" spans="2:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:13" ht="23.25" customHeight="1">
       <c r="B13" s="12"/>
       <c r="C13" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="42" t="s">
-        <v>37</v>
-      </c>
+      <c r="D13" s="42"/>
       <c r="E13" s="43"/>
       <c r="F13" s="58"/>
       <c r="G13" s="58"/>
@@ -1891,14 +1667,12 @@
       <c r="L13" s="75"/>
       <c r="M13" s="20"/>
     </row>
-    <row r="14" spans="2:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:13" ht="23.25" customHeight="1">
       <c r="B14" s="12"/>
       <c r="C14" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="D14" s="48" t="s">
-        <v>38</v>
-      </c>
+      <c r="D14" s="48"/>
       <c r="E14" s="6"/>
       <c r="F14" s="58"/>
       <c r="G14" s="58"/>
@@ -1909,14 +1683,12 @@
       <c r="L14" s="75"/>
       <c r="M14" s="20"/>
     </row>
-    <row r="15" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:13" ht="19" thickBot="1">
       <c r="B15" s="12"/>
       <c r="C15" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="46" t="s">
-        <v>52</v>
-      </c>
+      <c r="D15" s="46"/>
       <c r="E15" s="4"/>
       <c r="F15" s="59"/>
       <c r="G15" s="67"/>
@@ -1927,7 +1699,7 @@
       <c r="L15" s="80"/>
       <c r="M15" s="20"/>
     </row>
-    <row r="16" spans="2:13" ht="18" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:13" ht="20" thickBot="1">
       <c r="B16" s="12"/>
       <c r="C16" s="13" t="s">
         <v>1</v>
@@ -1961,51 +1733,23 @@
       </c>
       <c r="M16" s="20"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:14">
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
-      <c r="D17" s="87" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" s="61">
-        <v>3000000</v>
-      </c>
-      <c r="G17" s="69">
-        <f>E17*F17</f>
-        <v>3000000</v>
-      </c>
-      <c r="H17" s="72">
-        <v>45993</v>
-      </c>
-      <c r="I17" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="J17" s="73">
-        <v>1</v>
-      </c>
-      <c r="K17" s="61">
-        <v>2700000</v>
-      </c>
-      <c r="L17" s="82">
-        <f>J17*K17</f>
-        <v>2700000</v>
-      </c>
+      <c r="D17" s="87"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="72"/>
+      <c r="I17" s="73"/>
+      <c r="J17" s="73"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="82"/>
       <c r="M17" s="20"/>
     </row>
-    <row r="18" spans="2:14" ht="125" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:14">
       <c r="B18" s="12"/>
-      <c r="C18" s="93" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="91" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
+      <c r="C18" s="93"/>
+      <c r="D18" s="91"/>
       <c r="F18" s="61"/>
       <c r="G18" s="70"/>
       <c r="H18" s="72"/>
@@ -2015,17 +1759,10 @@
       <c r="L18" s="82"/>
       <c r="M18" s="82"/>
     </row>
-    <row r="19" spans="2:14" ht="75" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:14">
       <c r="B19" s="12"/>
-      <c r="C19" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="92" t="s">
-        <v>41</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
+      <c r="C19" s="93"/>
+      <c r="D19" s="92"/>
       <c r="F19" s="88"/>
       <c r="G19" s="70"/>
       <c r="H19" s="72"/>
@@ -2035,17 +1772,10 @@
       <c r="L19" s="82"/>
       <c r="M19" s="82"/>
     </row>
-    <row r="20" spans="2:14" ht="26" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:14">
       <c r="B20" s="12"/>
-      <c r="C20" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="D20" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
+      <c r="C20" s="93"/>
+      <c r="D20" s="51"/>
       <c r="F20" s="88"/>
       <c r="G20" s="70"/>
       <c r="H20" s="72"/>
@@ -2056,7 +1786,7 @@
       <c r="M20" s="82"/>
       <c r="N20" s="90"/>
     </row>
-    <row r="21" spans="2:14" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:14" ht="18" thickBot="1">
       <c r="B21" s="12"/>
       <c r="C21" s="50"/>
       <c r="D21" s="89"/>
@@ -2069,7 +1799,7 @@
       <c r="L21" s="82"/>
       <c r="M21" s="82"/>
     </row>
-    <row r="22" spans="2:14" ht="21.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:14" ht="21" thickBot="1">
       <c r="B22" s="12"/>
       <c r="C22" s="98" t="s">
         <v>9</v>
@@ -2078,7 +1808,7 @@
       <c r="E22" s="99"/>
       <c r="F22" s="100">
         <f>G17</f>
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="G22" s="101"/>
       <c r="H22" s="102" t="s">
@@ -2089,12 +1819,12 @@
       <c r="K22" s="104"/>
       <c r="L22" s="83">
         <f>L17</f>
-        <v>2700000</v>
+        <v>0</v>
       </c>
       <c r="M22" s="47"/>
       <c r="N22" s="86"/>
     </row>
-    <row r="23" spans="2:14" ht="21.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:14" ht="21" thickBot="1">
       <c r="B23" s="12"/>
       <c r="C23" s="49"/>
       <c r="D23" s="49"/>
@@ -2109,18 +1839,16 @@
       <c r="K23" s="104"/>
       <c r="L23" s="83">
         <f>L22*1.1</f>
-        <v>2970000.0000000005</v>
+        <v>0</v>
       </c>
       <c r="M23" s="47"/>
     </row>
-    <row r="24" spans="2:14" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:14" ht="19">
       <c r="B24" s="12"/>
       <c r="C24" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="105" t="s">
-        <v>44</v>
-      </c>
+      <c r="D24" s="105"/>
       <c r="E24" s="106"/>
       <c r="F24" s="106"/>
       <c r="G24" s="106"/>
@@ -2131,14 +1859,12 @@
       <c r="L24" s="106"/>
       <c r="M24" s="20"/>
     </row>
-    <row r="25" spans="2:14" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:14" ht="19">
       <c r="B25" s="12"/>
       <c r="C25" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="D25" s="38" t="s">
-        <v>45</v>
-      </c>
+      <c r="D25" s="38"/>
       <c r="E25" s="10"/>
       <c r="F25" s="63"/>
       <c r="G25" s="63"/>
@@ -2147,14 +1873,12 @@
       <c r="L25" s="77"/>
       <c r="M25" s="20"/>
     </row>
-    <row r="26" spans="2:14" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:14" ht="19">
       <c r="B26" s="12"/>
       <c r="C26" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="D26" s="107" t="s">
-        <v>46</v>
-      </c>
+      <c r="D26" s="107"/>
       <c r="E26" s="106"/>
       <c r="F26" s="106"/>
       <c r="G26" s="106"/>
@@ -2165,14 +1889,12 @@
       <c r="L26" s="106"/>
       <c r="M26" s="20"/>
     </row>
-    <row r="27" spans="2:14" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:14" ht="19">
       <c r="B27" s="12"/>
       <c r="C27" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="10" t="s">
-        <v>47</v>
-      </c>
+      <c r="D27" s="10"/>
       <c r="E27" s="10"/>
       <c r="F27" s="63"/>
       <c r="G27" s="63"/>
@@ -2183,7 +1905,7 @@
       <c r="L27" s="63"/>
       <c r="M27" s="20"/>
     </row>
-    <row r="28" spans="2:14" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:14" ht="18">
       <c r="B28" s="12"/>
       <c r="C28" s="33"/>
       <c r="D28" s="10"/>
@@ -2197,14 +1919,12 @@
       <c r="L28" s="63"/>
       <c r="M28" s="20"/>
     </row>
-    <row r="29" spans="2:14" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:14" ht="19">
       <c r="B29" s="12"/>
       <c r="C29" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="95" t="s">
-        <v>48</v>
-      </c>
+      <c r="D29" s="95"/>
       <c r="E29" s="95"/>
       <c r="F29" s="95"/>
       <c r="G29" s="95"/>
@@ -2215,14 +1935,12 @@
       <c r="L29" s="63"/>
       <c r="M29" s="20"/>
     </row>
-    <row r="30" spans="2:14" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:14" ht="19">
       <c r="B30" s="12"/>
       <c r="C30" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="95" t="s">
-        <v>49</v>
-      </c>
+      <c r="D30" s="95"/>
       <c r="E30" s="95"/>
       <c r="F30" s="95"/>
       <c r="G30" s="95"/>
@@ -2233,14 +1951,12 @@
       <c r="L30" s="63"/>
       <c r="M30" s="20"/>
     </row>
-    <row r="31" spans="2:14" ht="34" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:14" ht="19">
       <c r="B31" s="12"/>
       <c r="C31" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="27" t="s">
-        <v>50</v>
-      </c>
+      <c r="D31" s="27"/>
       <c r="E31" s="10"/>
       <c r="F31" s="63"/>
       <c r="G31" s="63"/>
@@ -2251,7 +1967,7 @@
       <c r="L31" s="63"/>
       <c r="M31" s="20"/>
     </row>
-    <row r="32" spans="2:14" ht="18" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:14" ht="19" thickBot="1">
       <c r="B32" s="12"/>
       <c r="C32" s="22"/>
       <c r="D32" s="94"/>
@@ -2265,7 +1981,7 @@
       <c r="L32" s="95"/>
       <c r="M32" s="20"/>
     </row>
-    <row r="33" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:16" ht="34.5" customHeight="1">
       <c r="B33" s="12"/>
       <c r="C33" s="11"/>
       <c r="D33" s="11"/>
@@ -2289,11 +2005,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="2:16" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:16" ht="63" customHeight="1" thickBot="1">
       <c r="B34" s="12"/>
-      <c r="C34" s="39" t="s">
-        <v>34</v>
-      </c>
+      <c r="C34" s="39"/>
       <c r="D34" s="40"/>
       <c r="E34" s="40"/>
       <c r="F34" s="65"/>
@@ -2307,7 +2021,7 @@
       <c r="L34" s="85"/>
       <c r="M34" s="20"/>
     </row>
-    <row r="35" spans="2:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:16" ht="18" thickBot="1">
       <c r="B35" s="14"/>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
@@ -2336,11 +2050,7 @@
     <mergeCell ref="D26:L26"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="D26" r:id="rId1" display="dhkim@servermate.net" xr:uid="{C0CCAAE0-7358-4CA7-8B0D-92A1BFA447B8}"/>
-  </hyperlinks>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="58" orientation="landscape" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup paperSize="9" scale="58" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>